--- a/language-data/japanese-radicals.xlsx
+++ b/language-data/japanese-radicals.xlsx
@@ -7913,7 +7913,7 @@
       </c>
       <c r="C183" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">𦉰 </t>
+          <t>𦉰</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
